--- a/New folder/Cube_finish.xlsx
+++ b/New folder/Cube_finish.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Warley Souza\Music\read_excel\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58272CEE-7658-4D92-BC41-C2DD15DF7161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF7894C-7643-4911-A303-8B57ADB94F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="877">
   <si>
     <t>Cube</t>
   </si>
@@ -2165,9 +2165,6 @@
   </si>
   <si>
     <t>87A</t>
-  </si>
-  <si>
-    <t>07/02//2022</t>
   </si>
   <si>
     <t>Second Floor Walls(E)(6-11)</t>
@@ -2662,7 +2659,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -2713,12 +2710,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3023,6 +3021,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J581"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -13596,11 +13597,11 @@
       <c r="A485" t="s">
         <v>714</v>
       </c>
-      <c r="B485" t="s">
+      <c r="B485" s="3">
+        <v>44599</v>
+      </c>
+      <c r="C485" t="s">
         <v>715</v>
-      </c>
-      <c r="C485" t="s">
-        <v>716</v>
       </c>
       <c r="D485" s="2">
         <v>44608</v>
@@ -13609,18 +13610,18 @@
         <v>2310</v>
       </c>
       <c r="F485" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
+        <v>717</v>
+      </c>
+      <c r="B486" s="3">
+        <v>44599</v>
+      </c>
+      <c r="C486" t="s">
         <v>718</v>
-      </c>
-      <c r="B486" t="s">
-        <v>715</v>
-      </c>
-      <c r="C486" t="s">
-        <v>719</v>
       </c>
       <c r="D486" s="2">
         <v>44627</v>
@@ -13634,13 +13635,13 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
+        <v>719</v>
+      </c>
+      <c r="B487" s="3">
+        <v>44599</v>
+      </c>
+      <c r="C487" t="s">
         <v>720</v>
-      </c>
-      <c r="B487" t="s">
-        <v>715</v>
-      </c>
-      <c r="C487" t="s">
-        <v>721</v>
       </c>
       <c r="D487" s="2">
         <v>44627</v>
@@ -13654,24 +13655,24 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
+        <v>721</v>
+      </c>
+      <c r="B488" s="3">
+        <v>44599</v>
+      </c>
+      <c r="C488" t="s">
         <v>722</v>
-      </c>
-      <c r="B488" t="s">
-        <v>715</v>
-      </c>
-      <c r="C488" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B489" s="2">
         <v>44600</v>
       </c>
       <c r="C489" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D489" s="2">
         <v>44608</v>
@@ -13680,18 +13681,18 @@
         <v>2350</v>
       </c>
       <c r="F489" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B490" s="2">
         <v>44600</v>
       </c>
       <c r="C490" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D490" s="2">
         <v>44628</v>
@@ -13705,13 +13706,13 @@
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B491" s="2">
         <v>44600</v>
       </c>
       <c r="C491" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D491" s="2">
         <v>44628</v>
@@ -13725,24 +13726,24 @@
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B492" s="2">
         <v>44600</v>
       </c>
       <c r="C492" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B493" s="2">
         <v>44600</v>
       </c>
       <c r="C493" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D493" s="2">
         <v>44608</v>
@@ -13751,18 +13752,18 @@
         <v>2360</v>
       </c>
       <c r="F493" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B494" s="2">
         <v>44600</v>
       </c>
       <c r="C494" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D494" s="2">
         <v>44628</v>
@@ -13776,13 +13777,13 @@
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B495" s="2">
         <v>44600</v>
       </c>
       <c r="C495" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D495" s="2">
         <v>44628</v>
@@ -13796,24 +13797,24 @@
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B496" s="2">
         <v>44600</v>
       </c>
       <c r="C496" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B497" s="2">
         <v>44601</v>
       </c>
       <c r="C497" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D497" s="2">
         <v>44608</v>
@@ -13822,69 +13823,69 @@
         <v>2390</v>
       </c>
       <c r="F497" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B498" s="2">
         <v>44601</v>
       </c>
       <c r="C498" t="s">
+        <v>741</v>
+      </c>
+      <c r="D498" t="s">
         <v>742</v>
       </c>
-      <c r="D498" t="s">
+      <c r="E498" t="s">
         <v>743</v>
       </c>
-      <c r="E498" t="s">
+      <c r="H498" t="s">
         <v>744</v>
-      </c>
-      <c r="H498" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B499" s="2">
         <v>44601</v>
       </c>
       <c r="C499" t="s">
+        <v>746</v>
+      </c>
+      <c r="D499" t="s">
+        <v>742</v>
+      </c>
+      <c r="E499" t="s">
         <v>747</v>
       </c>
-      <c r="D499" t="s">
-        <v>743</v>
-      </c>
-      <c r="E499" t="s">
+      <c r="H499" t="s">
         <v>748</v>
-      </c>
-      <c r="H499" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B500" s="2">
         <v>44601</v>
       </c>
       <c r="C500" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B501" s="2">
         <v>44602</v>
       </c>
       <c r="C501" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D501" s="2">
         <v>44616</v>
@@ -13898,64 +13899,64 @@
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B502" s="2">
         <v>44602</v>
       </c>
       <c r="C502" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D502" t="s">
         <v>598</v>
       </c>
       <c r="E502" t="s">
+        <v>753</v>
+      </c>
+      <c r="H502" t="s">
         <v>754</v>
-      </c>
-      <c r="H502" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B503" s="2">
         <v>44602</v>
       </c>
       <c r="C503" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D503" t="s">
         <v>598</v>
       </c>
       <c r="E503" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H503" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B504" s="2">
         <v>44602</v>
       </c>
       <c r="C504" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B505" s="2">
         <v>44603</v>
       </c>
       <c r="C505" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D505" s="2">
         <v>44615</v>
@@ -13969,13 +13970,13 @@
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B506" s="2">
         <v>44603</v>
       </c>
       <c r="C506" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D506" s="2">
         <v>44617</v>
@@ -13989,13 +13990,13 @@
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B507" s="2">
         <v>44603</v>
       </c>
       <c r="C507" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D507" t="s">
         <v>608</v>
@@ -14009,13 +14010,13 @@
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B508" s="2">
         <v>44603</v>
       </c>
       <c r="C508" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D508" t="s">
         <v>608</v>
@@ -14029,24 +14030,24 @@
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B509" s="2">
         <v>44603</v>
       </c>
       <c r="C509" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B510" s="2">
         <v>44606</v>
       </c>
       <c r="C510" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D510" s="2">
         <v>44615</v>
@@ -14060,13 +14061,13 @@
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B511" s="2">
         <v>44606</v>
       </c>
       <c r="C511" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D511" t="s">
         <v>617</v>
@@ -14080,13 +14081,13 @@
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B512" s="2">
         <v>44606</v>
       </c>
       <c r="C512" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D512" t="s">
         <v>617</v>
@@ -14100,35 +14101,35 @@
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B513" s="2">
         <v>44606</v>
       </c>
       <c r="C513" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B514" s="2">
         <v>44606</v>
       </c>
       <c r="C514" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B515" s="2">
         <v>44606</v>
       </c>
       <c r="C515" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D515" t="s">
         <v>617</v>
@@ -14142,13 +14143,13 @@
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B516" s="2">
         <v>44606</v>
       </c>
       <c r="C516" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D516" t="s">
         <v>617</v>
@@ -14162,793 +14163,793 @@
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B517" s="2">
         <v>44606</v>
       </c>
       <c r="C517" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B518" s="2">
         <v>44607</v>
       </c>
       <c r="C518" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D518" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E518" t="s">
         <v>599</v>
       </c>
       <c r="F518" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B519" s="2">
         <v>44607</v>
       </c>
       <c r="C519" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D519" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E519" t="s">
         <v>609</v>
       </c>
       <c r="H519" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B520" s="2">
         <v>44607</v>
       </c>
       <c r="C520" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D520" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E520" t="s">
         <v>599</v>
       </c>
       <c r="H520" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B521" s="2">
         <v>44607</v>
       </c>
       <c r="C521" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B522" s="2">
         <v>44608</v>
       </c>
       <c r="C522" t="s">
+        <v>783</v>
+      </c>
+      <c r="D522" t="s">
+        <v>742</v>
+      </c>
+      <c r="E522" t="s">
+        <v>753</v>
+      </c>
+      <c r="F522" t="s">
         <v>784</v>
-      </c>
-      <c r="D522" t="s">
-        <v>743</v>
-      </c>
-      <c r="E522" t="s">
-        <v>754</v>
-      </c>
-      <c r="F522" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B523" s="2">
         <v>44608</v>
       </c>
       <c r="C523" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B524" s="2">
         <v>44608</v>
       </c>
       <c r="C524" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B525" s="2">
         <v>44608</v>
       </c>
       <c r="C525" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B526" s="2">
         <v>44609</v>
       </c>
       <c r="C526" t="s">
+        <v>789</v>
+      </c>
+      <c r="D526" t="s">
+        <v>742</v>
+      </c>
+      <c r="E526" t="s">
+        <v>753</v>
+      </c>
+      <c r="F526" t="s">
         <v>790</v>
-      </c>
-      <c r="D526" t="s">
-        <v>743</v>
-      </c>
-      <c r="E526" t="s">
-        <v>754</v>
-      </c>
-      <c r="F526" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B527" s="2">
         <v>44609</v>
       </c>
       <c r="C527" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B528" s="2">
         <v>44609</v>
       </c>
       <c r="C528" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B529" s="2">
         <v>44609</v>
       </c>
       <c r="C529" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B530" s="2">
         <v>44610</v>
       </c>
       <c r="C530" t="s">
+        <v>795</v>
+      </c>
+      <c r="D530" t="s">
+        <v>742</v>
+      </c>
+      <c r="E530" t="s">
+        <v>753</v>
+      </c>
+      <c r="F530" t="s">
         <v>796</v>
-      </c>
-      <c r="D530" t="s">
-        <v>743</v>
-      </c>
-      <c r="E530" t="s">
-        <v>754</v>
-      </c>
-      <c r="F530" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B531" s="2">
         <v>44610</v>
       </c>
       <c r="C531" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B532" s="2">
         <v>44610</v>
       </c>
       <c r="C532" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B533" s="2">
         <v>44610</v>
       </c>
       <c r="C533" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B534" s="2">
         <v>44613</v>
       </c>
       <c r="C534" t="s">
+        <v>801</v>
+      </c>
+      <c r="D534" t="s">
+        <v>742</v>
+      </c>
+      <c r="E534" t="s">
         <v>802</v>
       </c>
-      <c r="D534" t="s">
-        <v>743</v>
-      </c>
-      <c r="E534" t="s">
+      <c r="F534" t="s">
         <v>803</v>
-      </c>
-      <c r="F534" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B535" s="2">
         <v>44613</v>
       </c>
       <c r="C535" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B536" s="2">
         <v>44613</v>
       </c>
       <c r="C536" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B537" s="2">
         <v>44613</v>
       </c>
       <c r="C537" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B538" s="2">
         <v>44614</v>
       </c>
       <c r="C538" t="s">
+        <v>808</v>
+      </c>
+      <c r="D538" t="s">
+        <v>742</v>
+      </c>
+      <c r="E538" t="s">
         <v>809</v>
       </c>
-      <c r="D538" t="s">
-        <v>743</v>
-      </c>
-      <c r="E538" t="s">
+      <c r="F538" t="s">
         <v>810</v>
-      </c>
-      <c r="F538" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B539" s="2">
         <v>44614</v>
       </c>
       <c r="C539" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B540" s="2">
         <v>44614</v>
       </c>
       <c r="C540" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B541" s="2">
         <v>44614</v>
       </c>
       <c r="C541" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B542" s="2">
         <v>44614</v>
       </c>
       <c r="C542" t="s">
+        <v>815</v>
+      </c>
+      <c r="D542" t="s">
+        <v>742</v>
+      </c>
+      <c r="E542" t="s">
+        <v>743</v>
+      </c>
+      <c r="F542" t="s">
         <v>816</v>
-      </c>
-      <c r="D542" t="s">
-        <v>743</v>
-      </c>
-      <c r="E542" t="s">
-        <v>744</v>
-      </c>
-      <c r="F542" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B543" s="2">
         <v>44614</v>
       </c>
       <c r="C543" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B544" s="2">
         <v>44614</v>
       </c>
       <c r="C544" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B545" s="2">
         <v>44614</v>
       </c>
       <c r="C545" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B546" s="2">
         <v>44615</v>
       </c>
       <c r="C546" t="s">
+        <v>821</v>
+      </c>
+      <c r="D546" t="s">
+        <v>742</v>
+      </c>
+      <c r="E546" t="s">
+        <v>802</v>
+      </c>
+      <c r="G546" t="s">
         <v>822</v>
-      </c>
-      <c r="D546" t="s">
-        <v>743</v>
-      </c>
-      <c r="E546" t="s">
-        <v>803</v>
-      </c>
-      <c r="G546" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B547" s="2">
         <v>44615</v>
       </c>
       <c r="C547" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B548" s="2">
         <v>44615</v>
       </c>
       <c r="C548" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B549" s="2">
         <v>44615</v>
       </c>
       <c r="C549" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B550" s="2">
         <v>44616</v>
       </c>
       <c r="C550" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D550" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E550" t="s">
         <v>609</v>
       </c>
       <c r="F550" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B551" s="2">
         <v>44616</v>
       </c>
       <c r="C551" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B552" s="2">
         <v>44616</v>
       </c>
       <c r="C552" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D552" t="s">
         <v>617</v>
       </c>
       <c r="E552" t="s">
+        <v>831</v>
+      </c>
+      <c r="H552" t="s">
         <v>832</v>
-      </c>
-      <c r="H552" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B553" s="2">
         <v>44616</v>
       </c>
       <c r="C553" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B554" s="2">
         <v>44617</v>
       </c>
       <c r="C554" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D554" t="s">
         <v>608</v>
       </c>
       <c r="E554" t="s">
+        <v>836</v>
+      </c>
+      <c r="G554" t="s">
         <v>837</v>
-      </c>
-      <c r="G554" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B555" s="2">
         <v>44617</v>
       </c>
       <c r="C555" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B556" s="2">
         <v>44617</v>
       </c>
       <c r="C556" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B557" s="2">
         <v>44617</v>
       </c>
       <c r="C557" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B558" s="2">
         <v>44620</v>
       </c>
       <c r="C558" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D558" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E558" t="s">
         <v>609</v>
       </c>
       <c r="F558" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B559" s="2">
         <v>44620</v>
       </c>
       <c r="C559" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B560" s="2">
         <v>44620</v>
       </c>
       <c r="C560" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B561" s="2">
         <v>44620</v>
       </c>
       <c r="C561" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B562" s="2">
         <v>44620</v>
       </c>
       <c r="C562" t="s">
+        <v>848</v>
+      </c>
+      <c r="D562" t="s">
+        <v>742</v>
+      </c>
+      <c r="E562" t="s">
+        <v>802</v>
+      </c>
+      <c r="F562" t="s">
         <v>849</v>
-      </c>
-      <c r="D562" t="s">
-        <v>743</v>
-      </c>
-      <c r="E562" t="s">
-        <v>803</v>
-      </c>
-      <c r="F562" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B563" s="2">
         <v>44620</v>
       </c>
       <c r="C563" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B564" s="2">
         <v>44620</v>
       </c>
       <c r="C564" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B565" s="2">
         <v>44620</v>
       </c>
       <c r="C565" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B566" s="2">
         <v>44621</v>
       </c>
       <c r="C566" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D566" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E566" t="s">
         <v>599</v>
       </c>
       <c r="F566" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B567" s="2">
         <v>44621</v>
       </c>
       <c r="C567" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B568" s="2">
         <v>44621</v>
       </c>
       <c r="C568" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B569" s="2">
         <v>44621</v>
       </c>
       <c r="C569" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B570" s="2">
         <v>44622</v>
       </c>
       <c r="C570" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D570" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E570" t="s">
         <v>609</v>
       </c>
       <c r="F570" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B571" s="2">
         <v>44622</v>
       </c>
       <c r="C571" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B572" s="2">
         <v>44622</v>
       </c>
       <c r="C572" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B573" s="2">
         <v>44622</v>
       </c>
       <c r="C573" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B574" s="2">
         <v>44623</v>
       </c>
       <c r="C574" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D574" t="s">
         <v>598</v>
@@ -14957,93 +14958,93 @@
         <v>599</v>
       </c>
       <c r="F574" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B575" s="2">
         <v>44623</v>
       </c>
       <c r="C575" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B576" s="2">
         <v>44623</v>
       </c>
       <c r="C576" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B577" s="2">
         <v>44623</v>
       </c>
       <c r="C577" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B578" s="2">
         <v>44624</v>
       </c>
       <c r="C578" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="D578" t="s">
         <v>608</v>
       </c>
       <c r="E578" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F578" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B579" s="2">
         <v>44624</v>
       </c>
       <c r="C579" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B580" s="2">
         <v>44624</v>
       </c>
       <c r="C580" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B581" s="2">
         <v>44624</v>
       </c>
       <c r="C581" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
   </sheetData>

--- a/New folder/Cube_finish.xlsx
+++ b/New folder/Cube_finish.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Warley Souza\Music\read_excel\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF7894C-7643-4911-A303-8B57ADB94F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C12526-1E9F-41A3-981F-C17DBE3165FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="876">
   <si>
     <t>Cube</t>
   </si>
@@ -794,9 +794,6 @@
   </si>
   <si>
     <t>Column(19)(J-H)C2</t>
-  </si>
-  <si>
-    <t>18//11/2021</t>
   </si>
   <si>
     <t>29D</t>
@@ -2658,9 +2655,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2715,8 +2709,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3022,20 +3018,21 @@
   <dimension ref="A1:J581"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -6044,7 +6041,7 @@
       <c r="C133" t="s">
         <v>190</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D133" s="2" t="s">
         <v>191</v>
       </c>
       <c r="E133">
@@ -6136,7 +6133,7 @@
       <c r="C137" t="s">
         <v>197</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D137" s="2" t="s">
         <v>191</v>
       </c>
       <c r="E137">
@@ -6343,7 +6340,7 @@
       <c r="C146" t="s">
         <v>197</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D146" s="2" t="s">
         <v>209</v>
       </c>
       <c r="E146">
@@ -6961,8 +6958,8 @@
       <c r="C173" t="s">
         <v>257</v>
       </c>
-      <c r="D173" t="s">
-        <v>258</v>
+      <c r="D173" s="2">
+        <v>44518</v>
       </c>
       <c r="E173">
         <v>2360</v>
@@ -6976,13 +6973,13 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B174" s="2">
         <v>44490</v>
       </c>
       <c r="C174" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D174" s="2">
         <v>44546</v>
@@ -6999,13 +6996,13 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B175" s="2">
         <v>44495</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D175" s="2">
         <v>44503</v>
@@ -7014,7 +7011,7 @@
         <v>2320</v>
       </c>
       <c r="F175" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J175" t="s">
         <v>12</v>
@@ -7022,13 +7019,13 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B176" s="2">
         <v>44495</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J176" t="s">
         <v>12</v>
@@ -7036,13 +7033,13 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B177" s="2">
         <v>44495</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J177" t="s">
         <v>12</v>
@@ -7050,13 +7047,13 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B178" s="2">
         <v>44495</v>
       </c>
       <c r="C178" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D178" s="2">
         <v>44551</v>
@@ -7073,13 +7070,13 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B179" s="2">
         <v>44496</v>
       </c>
       <c r="C179" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D179" s="2">
         <v>44503</v>
@@ -7096,13 +7093,13 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B180" s="2">
         <v>44496</v>
       </c>
       <c r="C180" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D180" s="2">
         <v>44524</v>
@@ -7119,13 +7116,13 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B181" s="2">
         <v>44496</v>
       </c>
       <c r="C181" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D181" s="2">
         <v>44524</v>
@@ -7142,13 +7139,13 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B182" s="2">
         <v>44496</v>
       </c>
       <c r="C182" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D182" s="2">
         <v>44552</v>
@@ -7165,13 +7162,13 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B183" s="2">
         <v>44496</v>
       </c>
       <c r="C183" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D183" s="2">
         <v>44503</v>
@@ -7188,13 +7185,13 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B184" s="2">
         <v>44496</v>
       </c>
       <c r="C184" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D184" s="2">
         <v>44524</v>
@@ -7211,13 +7208,13 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B185" s="2">
         <v>44496</v>
       </c>
       <c r="C185" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D185" s="2">
         <v>44524</v>
@@ -7234,13 +7231,13 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B186" s="2">
         <v>44496</v>
       </c>
       <c r="C186" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D186" s="2">
         <v>44552</v>
@@ -7257,13 +7254,13 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B187" s="2">
         <v>44496</v>
       </c>
       <c r="C187" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D187" s="2">
         <v>44503</v>
@@ -7280,13 +7277,13 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B188" s="2">
         <v>44496</v>
       </c>
       <c r="C188" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D188" s="2">
         <v>44524</v>
@@ -7303,13 +7300,13 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B189" s="2">
         <v>44496</v>
       </c>
       <c r="C189" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D189" s="2">
         <v>44524</v>
@@ -7326,13 +7323,13 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B190" s="2">
         <v>44496</v>
       </c>
       <c r="C190" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D190" s="2">
         <v>44552</v>
@@ -7349,13 +7346,13 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B191" s="2">
         <v>44497</v>
       </c>
       <c r="C191" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D191" s="2">
         <v>44504</v>
@@ -7372,13 +7369,13 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B192" s="2">
         <v>44497</v>
       </c>
       <c r="C192" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D192" s="2">
         <v>44525</v>
@@ -7395,13 +7392,13 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B193" s="2">
         <v>44497</v>
       </c>
       <c r="C193" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D193" s="2">
         <v>44525</v>
@@ -7418,13 +7415,13 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B194" s="2">
         <v>44497</v>
       </c>
       <c r="C194" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D194" s="2">
         <v>44553</v>
@@ -7441,13 +7438,13 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B195" s="2">
         <v>44501</v>
       </c>
       <c r="C195" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D195" s="2">
         <v>44510</v>
@@ -7456,7 +7453,7 @@
         <v>2340</v>
       </c>
       <c r="F195" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J195" t="s">
         <v>12</v>
@@ -7464,13 +7461,13 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B196" s="2">
         <v>44501</v>
       </c>
       <c r="C196" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D196" s="2">
         <v>44529</v>
@@ -7487,13 +7484,13 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B197" s="2">
         <v>44501</v>
       </c>
       <c r="C197" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D197" s="2">
         <v>44529</v>
@@ -7510,13 +7507,13 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B198" s="2">
         <v>44501</v>
       </c>
       <c r="C198" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D198" s="2">
         <v>44557</v>
@@ -7533,13 +7530,13 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B199" s="2">
         <v>44501</v>
       </c>
       <c r="C199" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D199" s="2">
         <v>44510</v>
@@ -7548,7 +7545,7 @@
         <v>2350</v>
       </c>
       <c r="F199" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J199" t="s">
         <v>12</v>
@@ -7556,13 +7553,13 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B200" s="2">
         <v>44501</v>
       </c>
       <c r="C200" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D200" s="2">
         <v>44529</v>
@@ -7579,13 +7576,13 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B201" s="2">
         <v>44501</v>
       </c>
       <c r="C201" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D201" s="2">
         <v>44529</v>
@@ -7602,13 +7599,13 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B202" s="2">
         <v>44501</v>
       </c>
       <c r="C202" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D202" s="2">
         <v>44557</v>
@@ -7625,13 +7622,13 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B203" s="2">
         <v>44501</v>
       </c>
       <c r="C203" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D203" s="2">
         <v>44510</v>
@@ -7648,13 +7645,13 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B204" s="2">
         <v>44501</v>
       </c>
       <c r="C204" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D204" s="2">
         <v>44529</v>
@@ -7668,13 +7665,13 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B205" s="2">
         <v>44502</v>
       </c>
       <c r="C205" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D205" s="2">
         <v>44510</v>
@@ -7683,7 +7680,7 @@
         <v>2320</v>
       </c>
       <c r="F205" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J205" t="s">
         <v>12</v>
@@ -7691,13 +7688,13 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B206" s="2">
         <v>44502</v>
       </c>
       <c r="C206" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D206" s="2">
         <v>44530</v>
@@ -7714,13 +7711,13 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B207" s="2">
         <v>44502</v>
       </c>
       <c r="C207" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D207" s="2">
         <v>44530</v>
@@ -7737,13 +7734,13 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B208" s="2">
         <v>44502</v>
       </c>
       <c r="C208" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D208" s="2">
         <v>44558</v>
@@ -7760,13 +7757,13 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B209" s="2">
         <v>44503</v>
       </c>
       <c r="C209" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D209" s="2">
         <v>44510</v>
@@ -7783,13 +7780,13 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B210" s="2">
         <v>44503</v>
       </c>
       <c r="C210" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D210" s="2">
         <v>44531</v>
@@ -7806,13 +7803,13 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B211" s="2">
         <v>44503</v>
       </c>
       <c r="C211" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D211" s="2">
         <v>44531</v>
@@ -7829,13 +7826,13 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B212" s="2">
         <v>44503</v>
       </c>
       <c r="C212" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D212" s="2">
         <v>44559</v>
@@ -7852,13 +7849,13 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B213" s="2">
         <v>44504</v>
       </c>
       <c r="C213" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D213" s="2">
         <v>44511</v>
@@ -7875,13 +7872,13 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B214" s="2">
         <v>44504</v>
       </c>
       <c r="C214" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D214" s="2">
         <v>44532</v>
@@ -7898,13 +7895,13 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B215" s="2">
         <v>44504</v>
       </c>
       <c r="C215" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D215" s="2">
         <v>44532</v>
@@ -7921,13 +7918,13 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B216" s="2">
         <v>44504</v>
       </c>
       <c r="C216" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D216" s="2">
         <v>44540</v>
@@ -7944,13 +7941,13 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B217" s="2">
         <v>44504</v>
       </c>
       <c r="C217" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D217" s="2">
         <v>44511</v>
@@ -7967,13 +7964,13 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B218" s="2">
         <v>44504</v>
       </c>
       <c r="C218" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D218" s="2">
         <v>44532</v>
@@ -7990,13 +7987,13 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B219" s="2">
         <v>44504</v>
       </c>
       <c r="C219" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D219" s="2">
         <v>44532</v>
@@ -8013,13 +8010,13 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B220" s="2">
         <v>44504</v>
       </c>
       <c r="C220" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D220" s="2">
         <v>44560</v>
@@ -8036,13 +8033,13 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B221" s="2">
         <v>44504</v>
       </c>
       <c r="C221" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D221" s="2">
         <v>44511</v>
@@ -8059,13 +8056,13 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B222" s="2">
         <v>44504</v>
       </c>
       <c r="C222" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D222" s="2">
         <v>44532</v>
@@ -8082,13 +8079,13 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B223" s="2">
         <v>44504</v>
       </c>
       <c r="C223" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D223" s="2">
         <v>44532</v>
@@ -8105,13 +8102,13 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B224" s="2">
         <v>44504</v>
       </c>
       <c r="C224" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D224" s="2">
         <v>44560</v>
@@ -8128,13 +8125,13 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B225" s="2">
         <v>44505</v>
       </c>
       <c r="C225" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D225" s="2">
         <v>44512</v>
@@ -8151,13 +8148,13 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B226" s="2">
         <v>44505</v>
       </c>
       <c r="C226" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D226" s="2">
         <v>44533</v>
@@ -8174,13 +8171,13 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B227" s="2">
         <v>44505</v>
       </c>
       <c r="C227" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D227" s="2">
         <v>44533</v>
@@ -8197,13 +8194,13 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B228" s="2">
         <v>44505</v>
       </c>
       <c r="C228" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D228" s="2">
         <v>44561</v>
@@ -8212,7 +8209,7 @@
         <v>2370</v>
       </c>
       <c r="I228" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J228" t="s">
         <v>12</v>
@@ -8220,13 +8217,13 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B229" s="2">
         <v>44508</v>
       </c>
       <c r="C229" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D229" s="2">
         <v>44517</v>
@@ -8235,7 +8232,7 @@
         <v>2330</v>
       </c>
       <c r="F229" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J229" t="s">
         <v>12</v>
@@ -8243,13 +8240,13 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B230" s="2">
         <v>44508</v>
       </c>
       <c r="C230" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D230" s="2">
         <v>44536</v>
@@ -8266,13 +8263,13 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B231" s="2">
         <v>44508</v>
       </c>
       <c r="C231" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D231" s="2">
         <v>44536</v>
@@ -8289,13 +8286,13 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B232" s="2">
         <v>44508</v>
       </c>
       <c r="C232" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D232" s="2">
         <v>44565</v>
@@ -8312,13 +8309,13 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B233" s="2">
         <v>44509</v>
       </c>
       <c r="C233" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D233" s="2">
         <v>44517</v>
@@ -8327,7 +8324,7 @@
         <v>2330</v>
       </c>
       <c r="F233" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J233" t="s">
         <v>12</v>
@@ -8335,13 +8332,13 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B234" s="2">
         <v>44510</v>
       </c>
       <c r="C234" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D234" s="2">
         <v>44537</v>
@@ -8358,13 +8355,13 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B235" s="2">
         <v>44511</v>
       </c>
       <c r="C235" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D235" s="2">
         <v>44537</v>
@@ -8381,13 +8378,13 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B236" s="2">
         <v>44512</v>
       </c>
       <c r="C236" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D236" s="2">
         <v>44565</v>
@@ -8404,13 +8401,13 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B237" s="2">
         <v>44513</v>
       </c>
       <c r="C237" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D237" s="2">
         <v>44517</v>
@@ -8419,7 +8416,7 @@
         <v>2340</v>
       </c>
       <c r="F237" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J237" t="s">
         <v>12</v>
@@ -8427,13 +8424,13 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B238" s="2">
         <v>44514</v>
       </c>
       <c r="C238" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D238" s="2">
         <v>44537</v>
@@ -8450,13 +8447,13 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B239" s="2">
         <v>44515</v>
       </c>
       <c r="C239" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D239" s="2">
         <v>44537</v>
@@ -8473,13 +8470,13 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B240" s="2">
         <v>44516</v>
       </c>
       <c r="C240" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D240" s="2">
         <v>44565</v>
@@ -8496,13 +8493,13 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B241" s="2">
         <v>44517</v>
       </c>
       <c r="C241" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D241" s="2">
         <v>44517</v>
@@ -8511,7 +8508,7 @@
         <v>2360</v>
       </c>
       <c r="F241" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J241" t="s">
         <v>12</v>
@@ -8519,13 +8516,13 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B242" s="2">
         <v>44518</v>
       </c>
       <c r="C242" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D242" s="2">
         <v>44537</v>
@@ -8542,13 +8539,13 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B243" s="2">
         <v>44519</v>
       </c>
       <c r="C243" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J243" t="s">
         <v>12</v>
@@ -8556,13 +8553,13 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B244" s="2">
         <v>44520</v>
       </c>
       <c r="C244" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D244" s="2">
         <v>44565</v>
@@ -8579,13 +8576,13 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B245" s="2">
         <v>44510</v>
       </c>
       <c r="C245" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D245" s="2">
         <v>44518</v>
@@ -8602,13 +8599,13 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B246" s="2">
         <v>44510</v>
       </c>
       <c r="C246" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D246" s="2">
         <v>44538</v>
@@ -8625,13 +8622,13 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B247" s="2">
         <v>44510</v>
       </c>
       <c r="C247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D247" s="2">
         <v>44538</v>
@@ -8648,13 +8645,13 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B248" s="2">
         <v>44510</v>
       </c>
       <c r="C248" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D248" s="2">
         <v>44566</v>
@@ -8671,13 +8668,13 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B249" s="2">
         <v>44511</v>
       </c>
       <c r="C249" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D249" s="2">
         <v>44518</v>
@@ -8694,13 +8691,13 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B250" s="2">
         <v>44511</v>
       </c>
       <c r="C250" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D250" s="2">
         <v>44539</v>
@@ -8717,13 +8714,13 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B251" s="2">
         <v>44511</v>
       </c>
       <c r="C251" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D251" s="2">
         <v>44539</v>
@@ -8740,13 +8737,13 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B252" s="2">
         <v>44511</v>
       </c>
       <c r="C252" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D252" s="2">
         <v>44567</v>
@@ -8763,13 +8760,13 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B253" s="2">
         <v>44512</v>
       </c>
       <c r="C253" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D253" s="2">
         <v>44526</v>
@@ -8786,13 +8783,13 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B254" s="2">
         <v>44512</v>
       </c>
       <c r="C254" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D254" s="2">
         <v>44540</v>
@@ -8809,13 +8806,13 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B255" s="2">
         <v>44512</v>
       </c>
       <c r="C255" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D255" s="2">
         <v>44540</v>
@@ -8832,13 +8829,13 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B256" s="2">
         <v>44512</v>
       </c>
       <c r="C256" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D256" s="2">
         <v>44568</v>
@@ -8855,13 +8852,13 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B257" s="2">
         <v>44515</v>
       </c>
       <c r="C257" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D257" s="2">
         <v>44524</v>
@@ -8878,13 +8875,13 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B258" s="2">
         <v>44515</v>
       </c>
       <c r="C258" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D258" s="2">
         <v>44543</v>
@@ -8901,13 +8898,13 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B259" s="2">
         <v>44515</v>
       </c>
       <c r="C259" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D259" s="2">
         <v>44543</v>
@@ -8924,13 +8921,13 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B260" s="2">
         <v>44515</v>
       </c>
       <c r="C260" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D260" s="2">
         <v>44571</v>
@@ -8947,13 +8944,13 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B261" s="2">
         <v>44516</v>
       </c>
       <c r="C261" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D261" s="2">
         <v>44524</v>
@@ -8970,13 +8967,13 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B262" s="2">
         <v>44516</v>
       </c>
       <c r="C262" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D262" s="2">
         <v>44544</v>
@@ -8993,13 +8990,13 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B263" s="2">
         <v>44516</v>
       </c>
       <c r="C263" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D263" s="2">
         <v>44544</v>
@@ -9016,13 +9013,13 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B264" s="2">
         <v>44516</v>
       </c>
       <c r="C264" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D264" s="2">
         <v>44572</v>
@@ -9039,13 +9036,13 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B265" s="2">
         <v>44516</v>
       </c>
       <c r="C265" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D265" s="2">
         <v>44524</v>
@@ -9062,13 +9059,13 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B266" s="2">
         <v>44516</v>
       </c>
       <c r="C266" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D266" s="2">
         <v>44544</v>
@@ -9085,13 +9082,13 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B267" s="2">
         <v>44516</v>
       </c>
       <c r="C267" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D267" s="2">
         <v>44544</v>
@@ -9108,13 +9105,13 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B268" s="2">
         <v>44516</v>
       </c>
       <c r="C268" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D268" s="2">
         <v>44572</v>
@@ -9131,13 +9128,13 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B269" s="2">
         <v>44516</v>
       </c>
       <c r="C269" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D269" s="2">
         <v>44524</v>
@@ -9154,13 +9151,13 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B270" s="2">
         <v>44516</v>
       </c>
       <c r="C270" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D270" s="2">
         <v>44544</v>
@@ -9177,13 +9174,13 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B271" s="2">
         <v>44516</v>
       </c>
       <c r="C271" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D271" s="2">
         <v>44544</v>
@@ -9200,13 +9197,13 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B272" s="2">
         <v>44516</v>
       </c>
       <c r="C272" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D272" s="2">
         <v>44572</v>
@@ -9223,13 +9220,13 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B273" s="2">
         <v>44516</v>
       </c>
       <c r="C273" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D273" s="2">
         <v>44524</v>
@@ -9246,13 +9243,13 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B274" s="2">
         <v>44516</v>
       </c>
       <c r="C274" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D274" s="2">
         <v>44544</v>
@@ -9269,13 +9266,13 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B275" s="2">
         <v>44516</v>
       </c>
       <c r="C275" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J275" t="s">
         <v>12</v>
@@ -9283,13 +9280,13 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B276" s="2">
         <v>44516</v>
       </c>
       <c r="C276" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D276" s="2">
         <v>44572</v>
@@ -9306,13 +9303,13 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B277" s="2">
         <v>44518</v>
       </c>
       <c r="C277" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D277" s="2">
         <v>44525</v>
@@ -9329,13 +9326,13 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B278" s="2">
         <v>44518</v>
       </c>
       <c r="C278" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D278" s="2">
         <v>44546</v>
@@ -9352,13 +9349,13 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B279" s="2">
         <v>44518</v>
       </c>
       <c r="C279" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D279" s="2">
         <v>44546</v>
@@ -9375,13 +9372,13 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B280" s="2">
         <v>44518</v>
       </c>
       <c r="C280" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D280" s="2">
         <v>44575</v>
@@ -9398,13 +9395,13 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B281" s="2">
         <v>44519</v>
       </c>
       <c r="C281" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D281" s="2">
         <v>44526</v>
@@ -9421,13 +9418,13 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B282" s="2">
         <v>44519</v>
       </c>
       <c r="C282" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D282" s="2">
         <v>44547</v>
@@ -9444,13 +9441,13 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B283" s="2">
         <v>44519</v>
       </c>
       <c r="C283" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D283" s="2">
         <v>44547</v>
@@ -9467,13 +9464,13 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B284" s="2">
         <v>44519</v>
       </c>
       <c r="C284" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J284" t="s">
         <v>12</v>
@@ -9481,13 +9478,13 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B285" s="2">
         <v>44523</v>
       </c>
       <c r="C285" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D285" s="2">
         <v>44531</v>
@@ -9504,13 +9501,13 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B286" s="2">
         <v>44523</v>
       </c>
       <c r="C286" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D286" s="2">
         <v>44551</v>
@@ -9527,13 +9524,13 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B287" s="2">
         <v>44523</v>
       </c>
       <c r="C287" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D287" s="2">
         <v>44551</v>
@@ -9550,13 +9547,13 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B288" s="2">
         <v>44523</v>
       </c>
       <c r="C288" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D288" s="2">
         <v>44579</v>
@@ -9573,13 +9570,13 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B289" s="2">
         <v>44523</v>
       </c>
       <c r="C289" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D289" s="2">
         <v>44531</v>
@@ -9596,13 +9593,13 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B290" s="2">
         <v>44523</v>
       </c>
       <c r="C290" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D290" s="2">
         <v>44551</v>
@@ -9619,13 +9616,13 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B291" s="2">
         <v>44523</v>
       </c>
       <c r="C291" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D291" s="2">
         <v>44551</v>
@@ -9642,13 +9639,13 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B292" s="2">
         <v>44523</v>
       </c>
       <c r="C292" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D292" s="2">
         <v>44579</v>
@@ -9665,13 +9662,13 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B293" s="2">
         <v>44523</v>
       </c>
       <c r="C293" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D293" s="2">
         <v>44531</v>
@@ -9688,13 +9685,13 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B294" s="2">
         <v>44523</v>
       </c>
       <c r="C294" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D294" s="2">
         <v>44551</v>
@@ -9711,13 +9708,13 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B295" s="2">
         <v>44523</v>
       </c>
       <c r="C295" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D295" s="2">
         <v>44551</v>
@@ -9734,13 +9731,13 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B296" s="2">
         <v>44523</v>
       </c>
       <c r="C296" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D296" s="2">
         <v>44579</v>
@@ -9757,13 +9754,13 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B297" s="2">
         <v>44523</v>
       </c>
       <c r="C297" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D297" s="2">
         <v>44531</v>
@@ -9780,13 +9777,13 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B298" s="2">
         <v>44523</v>
       </c>
       <c r="C298" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D298" s="2">
         <v>44551</v>
@@ -9803,13 +9800,13 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B299" s="2">
         <v>44523</v>
       </c>
       <c r="C299" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J299" t="s">
         <v>12</v>
@@ -9817,13 +9814,13 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B300" s="2">
         <v>44523</v>
       </c>
       <c r="C300" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D300" s="2">
         <v>44579</v>
@@ -9840,13 +9837,13 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B301" s="2">
         <v>44524</v>
       </c>
       <c r="C301" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D301" s="2">
         <v>44531</v>
@@ -9863,13 +9860,13 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B302" s="2">
         <v>44524</v>
       </c>
       <c r="C302" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D302" s="2">
         <v>44552</v>
@@ -9886,13 +9883,13 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B303" s="2">
         <v>44524</v>
       </c>
       <c r="C303" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D303" s="2">
         <v>44552</v>
@@ -9909,13 +9906,13 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B304" s="2">
         <v>44524</v>
       </c>
       <c r="C304" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D304" s="2">
         <v>44580</v>
@@ -9932,13 +9929,13 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B305" s="2">
         <v>44525</v>
       </c>
       <c r="C305" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D305" s="2">
         <v>44532</v>
@@ -9955,13 +9952,13 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B306" s="2">
         <v>44525</v>
       </c>
       <c r="C306" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D306" s="2">
         <v>44553</v>
@@ -9978,13 +9975,13 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B307" s="2">
         <v>44525</v>
       </c>
       <c r="C307" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D307" s="2">
         <v>44553</v>
@@ -10001,13 +9998,13 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B308" s="2">
         <v>44525</v>
       </c>
       <c r="C308" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D308" s="2">
         <v>44581</v>
@@ -10024,13 +10021,13 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B309" s="2">
         <v>44529</v>
       </c>
       <c r="C309" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D309" s="2">
         <v>44538</v>
@@ -10039,7 +10036,7 @@
         <v>2390</v>
       </c>
       <c r="F309" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="J309" t="s">
         <v>12</v>
@@ -10047,13 +10044,13 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B310" s="2">
         <v>44529</v>
       </c>
       <c r="C310" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D310" s="2">
         <v>44557</v>
@@ -10070,13 +10067,13 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B311" s="2">
         <v>44529</v>
       </c>
       <c r="C311" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D311" s="2">
         <v>44557</v>
@@ -10093,13 +10090,13 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B312" s="2">
         <v>44529</v>
       </c>
       <c r="C312" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D312" s="2">
         <v>44585</v>
@@ -10116,13 +10113,13 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B313" s="2">
         <v>44529</v>
       </c>
       <c r="C313" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D313" s="2">
         <v>44585</v>
@@ -10139,13 +10136,13 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B314" s="2">
         <v>44530</v>
       </c>
       <c r="C314" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D314" s="2">
         <v>44538</v>
@@ -10154,7 +10151,7 @@
         <v>2360</v>
       </c>
       <c r="F314" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="J314" t="s">
         <v>12</v>
@@ -10162,13 +10159,13 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B315" s="2">
         <v>44530</v>
       </c>
       <c r="C315" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D315" s="2">
         <v>44558</v>
@@ -10185,13 +10182,13 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B316" s="2">
         <v>44530</v>
       </c>
       <c r="C316" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D316" s="2">
         <v>44558</v>
@@ -10208,13 +10205,13 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B317" s="2">
         <v>44530</v>
       </c>
       <c r="C317" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D317" s="2">
         <v>44586</v>
@@ -10231,13 +10228,13 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B318" s="2">
         <v>44530</v>
       </c>
       <c r="C318" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D318" s="2">
         <v>44586</v>
@@ -10254,13 +10251,13 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B319" s="2">
         <v>44541</v>
       </c>
       <c r="C319" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D319" s="2">
         <v>44538</v>
@@ -10277,13 +10274,13 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B320" s="2">
         <v>44541</v>
       </c>
       <c r="C320" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D320" s="2">
         <v>44559</v>
@@ -10300,13 +10297,13 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B321" s="2">
         <v>44541</v>
       </c>
       <c r="C321" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D321" s="2">
         <v>44559</v>
@@ -10323,13 +10320,13 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B322" s="2">
         <v>44541</v>
       </c>
       <c r="C322" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D322" s="2">
         <v>44587</v>
@@ -10346,13 +10343,13 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B323" s="2">
         <v>44541</v>
       </c>
       <c r="C323" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D323" s="2">
         <v>44538</v>
@@ -10369,13 +10366,13 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B324" s="2">
         <v>44541</v>
       </c>
       <c r="C324" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D324" s="2">
         <v>44559</v>
@@ -10392,13 +10389,13 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B325" s="2">
         <v>44541</v>
       </c>
       <c r="C325" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D325" s="2">
         <v>44559</v>
@@ -10415,13 +10412,13 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B326" s="2">
         <v>44541</v>
       </c>
       <c r="C326" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D326" s="2">
         <v>44587</v>
@@ -10438,13 +10435,13 @@
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B327" s="2">
         <v>44541</v>
       </c>
       <c r="C327" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D327" s="2">
         <v>44538</v>
@@ -10461,13 +10458,13 @@
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B328" s="2">
         <v>44541</v>
       </c>
       <c r="C328" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D328" s="2">
         <v>44559</v>
@@ -10484,13 +10481,13 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B329" s="2">
         <v>44541</v>
       </c>
       <c r="C329" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D329" s="2">
         <v>44559</v>
@@ -10507,13 +10504,13 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B330" s="2">
         <v>44541</v>
       </c>
       <c r="C330" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D330" s="2">
         <v>44587</v>
@@ -10530,13 +10527,13 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B331" s="2">
         <v>44541</v>
       </c>
       <c r="C331" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D331" s="2">
         <v>44538</v>
@@ -10553,13 +10550,13 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B332" s="2">
         <v>44541</v>
       </c>
       <c r="C332" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D332" s="2">
         <v>44559</v>
@@ -10576,13 +10573,13 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B333" s="2">
         <v>44541</v>
       </c>
       <c r="C333" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D333" s="2">
         <v>44559</v>
@@ -10599,13 +10596,13 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B334" s="2">
         <v>44541</v>
       </c>
       <c r="C334" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D334" s="2">
         <v>44587</v>
@@ -10622,13 +10619,13 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B335" s="2">
         <v>44532</v>
       </c>
       <c r="C335" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D335" s="2">
         <v>44539</v>
@@ -10645,13 +10642,13 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B336" s="2">
         <v>44532</v>
       </c>
       <c r="C336" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D336" s="2">
         <v>44560</v>
@@ -10668,13 +10665,13 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B337" s="2">
         <v>44532</v>
       </c>
       <c r="C337" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D337" s="2">
         <v>44560</v>
@@ -10691,13 +10688,13 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B338" s="2">
         <v>44532</v>
       </c>
       <c r="C338" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D338" s="2">
         <v>44588</v>
@@ -10714,13 +10711,13 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B339" s="2">
         <v>44533</v>
       </c>
       <c r="C339" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D339" s="2">
         <v>44547</v>
@@ -10737,13 +10734,13 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B340" s="2">
         <v>44533</v>
       </c>
       <c r="C340" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D340" s="2">
         <v>44561</v>
@@ -10760,13 +10757,13 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B341" s="2">
         <v>44533</v>
       </c>
       <c r="C341" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D341" s="2">
         <v>44561</v>
@@ -10783,13 +10780,13 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B342" s="2">
         <v>44533</v>
       </c>
       <c r="C342" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D342" s="2">
         <v>44589</v>
@@ -10806,13 +10803,13 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B343" s="2">
         <v>44536</v>
       </c>
       <c r="C343" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D343" s="2">
         <v>44545</v>
@@ -10821,7 +10818,7 @@
         <v>2380</v>
       </c>
       <c r="F343" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J343" t="s">
         <v>12</v>
@@ -10829,13 +10826,13 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B344" s="2">
         <v>44536</v>
       </c>
       <c r="C344" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D344" s="2">
         <v>44565</v>
@@ -10852,13 +10849,13 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B345" s="2">
         <v>44536</v>
       </c>
       <c r="C345" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D345" s="2">
         <v>44565</v>
@@ -10872,13 +10869,13 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B346" s="2">
         <v>44536</v>
       </c>
       <c r="C346" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D346" s="2">
         <v>44592</v>
@@ -10895,13 +10892,13 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B347" s="2">
         <v>44538</v>
       </c>
       <c r="C347" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D347" s="2">
         <v>44545</v>
@@ -10918,13 +10915,13 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B348" s="2">
         <v>44538</v>
       </c>
       <c r="C348" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D348" s="2">
         <v>44566</v>
@@ -10941,13 +10938,13 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B349" s="2">
         <v>44538</v>
       </c>
       <c r="C349" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D349" s="2">
         <v>44566</v>
@@ -10964,13 +10961,13 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B350" s="2">
         <v>44538</v>
       </c>
       <c r="C350" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D350" s="2">
         <v>44594</v>
@@ -10987,13 +10984,13 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B351" s="2">
         <v>44539</v>
       </c>
       <c r="C351" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D351" s="2">
         <v>44546</v>
@@ -11010,13 +11007,13 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B352" s="2">
         <v>44539</v>
       </c>
       <c r="C352" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D352" s="2">
         <v>44567</v>
@@ -11033,13 +11030,13 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B353" s="2">
         <v>44539</v>
       </c>
       <c r="C353" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D353" s="2">
         <v>44567</v>
@@ -11056,13 +11053,13 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B354" s="2">
         <v>44539</v>
       </c>
       <c r="C354" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D354" s="2">
         <v>44595</v>
@@ -11076,13 +11073,13 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B355" s="2">
         <v>44540</v>
       </c>
       <c r="C355" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D355" s="2">
         <v>44547</v>
@@ -11096,13 +11093,13 @@
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B356" s="2">
         <v>44540</v>
       </c>
       <c r="C356" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D356" s="2">
         <v>44568</v>
@@ -11119,13 +11116,13 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B357" s="2">
         <v>44540</v>
       </c>
       <c r="C357" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D357" s="2">
         <v>44568</v>
@@ -11142,13 +11139,13 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B358" s="2">
         <v>44540</v>
       </c>
       <c r="C358" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D358" s="2">
         <v>44596</v>
@@ -11165,13 +11162,13 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B359" s="2">
         <v>44543</v>
       </c>
       <c r="C359" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D359" s="2">
         <v>44552</v>
@@ -11180,7 +11177,7 @@
         <v>2330</v>
       </c>
       <c r="F359" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J359" t="s">
         <v>12</v>
@@ -11188,13 +11185,13 @@
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B360" s="2">
         <v>44543</v>
       </c>
       <c r="C360" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D360" s="2">
         <v>44571</v>
@@ -11211,13 +11208,13 @@
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B361" s="2">
         <v>44543</v>
       </c>
       <c r="C361" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D361" s="2">
         <v>44571</v>
@@ -11234,13 +11231,13 @@
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B362" s="2">
         <v>44543</v>
       </c>
       <c r="C362" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D362" s="2">
         <v>44599</v>
@@ -11257,13 +11254,13 @@
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B363" s="2">
         <v>44544</v>
       </c>
       <c r="C363" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D363" s="2">
         <v>44552</v>
@@ -11280,13 +11277,13 @@
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B364" s="2">
         <v>44544</v>
       </c>
       <c r="C364" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D364" s="2">
         <v>44572</v>
@@ -11303,13 +11300,13 @@
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B365" s="2">
         <v>44544</v>
       </c>
       <c r="C365" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D365" s="2">
         <v>44572</v>
@@ -11326,13 +11323,13 @@
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B366" s="2">
         <v>44544</v>
       </c>
       <c r="C366" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D366" s="2">
         <v>44600</v>
@@ -11349,13 +11346,13 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B367" s="2">
         <v>44545</v>
       </c>
       <c r="C367" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D367" s="2">
         <v>44552</v>
@@ -11364,7 +11361,7 @@
         <v>2380</v>
       </c>
       <c r="F367" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="J367" t="s">
         <v>12</v>
@@ -11372,13 +11369,13 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B368" s="2">
         <v>44545</v>
       </c>
       <c r="C368" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D368" s="2">
         <v>44573</v>
@@ -11395,13 +11392,13 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B369" s="2">
         <v>44545</v>
       </c>
       <c r="C369" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D369" s="2">
         <v>44573</v>
@@ -11418,13 +11415,13 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B370" s="2">
         <v>44545</v>
       </c>
       <c r="C370" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D370" s="2">
         <v>44601</v>
@@ -11441,13 +11438,13 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B371" s="2">
         <v>44546</v>
       </c>
       <c r="C371" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D371" s="2">
         <v>44553</v>
@@ -11464,13 +11461,13 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B372" s="2">
         <v>44546</v>
       </c>
       <c r="C372" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D372" s="2">
         <v>44574</v>
@@ -11487,13 +11484,13 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B373" s="2">
         <v>44546</v>
       </c>
       <c r="C373" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D373" s="2">
         <v>44574</v>
@@ -11510,13 +11507,13 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B374" s="2">
         <v>44546</v>
       </c>
       <c r="C374" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D374" s="2">
         <v>44602</v>
@@ -11533,13 +11530,13 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B375" s="2">
         <v>44547</v>
       </c>
       <c r="C375" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D375" s="2">
         <v>44554</v>
@@ -11551,18 +11548,18 @@
         <v>33.299999999999997</v>
       </c>
       <c r="J375" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B376" s="2">
         <v>44547</v>
       </c>
       <c r="C376" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D376" s="2">
         <v>44575</v>
@@ -11574,18 +11571,18 @@
         <v>51.8</v>
       </c>
       <c r="J376" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B377" s="2">
         <v>44547</v>
       </c>
       <c r="C377" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D377" s="2">
         <v>44575</v>
@@ -11597,18 +11594,18 @@
         <v>51.7</v>
       </c>
       <c r="J377" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B378" s="2">
         <v>44547</v>
       </c>
       <c r="C378" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D378" s="2">
         <v>44603</v>
@@ -11620,18 +11617,18 @@
         <v>59.6</v>
       </c>
       <c r="J378" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B379" s="2">
         <v>44547</v>
       </c>
       <c r="C379" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D379" s="2">
         <v>44554</v>
@@ -11643,18 +11640,18 @@
         <v>29.3</v>
       </c>
       <c r="J379" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B380" s="2">
         <v>44547</v>
       </c>
       <c r="C380" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D380" s="2">
         <v>44575</v>
@@ -11666,18 +11663,18 @@
         <v>45.8</v>
       </c>
       <c r="J380" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B381" s="2">
         <v>44547</v>
       </c>
       <c r="C381" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D381" s="2">
         <v>44603</v>
@@ -11689,18 +11686,18 @@
         <v>53.9</v>
       </c>
       <c r="J381" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B382" s="2">
         <v>44547</v>
       </c>
       <c r="C382" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D382" s="2">
         <v>44575</v>
@@ -11714,13 +11711,13 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B383" s="2">
         <v>44550</v>
       </c>
       <c r="C383" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D383" s="2">
         <v>44578</v>
@@ -11732,18 +11729,18 @@
         <v>36.299999999999997</v>
       </c>
       <c r="J383" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B384" s="2">
         <v>44550</v>
       </c>
       <c r="C384" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D384" s="2">
         <v>44578</v>
@@ -11755,18 +11752,18 @@
         <v>35.299999999999997</v>
       </c>
       <c r="J384" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B385" s="2">
         <v>44550</v>
       </c>
       <c r="C385" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D385" s="2">
         <v>44578</v>
@@ -11778,18 +11775,18 @@
         <v>39.5</v>
       </c>
       <c r="J385" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B386" s="2">
         <v>44550</v>
       </c>
       <c r="C386" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D386" s="2">
         <v>44606</v>
@@ -11801,18 +11798,18 @@
         <v>37.299999999999997</v>
       </c>
       <c r="J386" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B387" s="2">
         <v>44566</v>
       </c>
       <c r="C387" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D387" s="2">
         <v>44582</v>
@@ -11821,21 +11818,21 @@
         <v>2380</v>
       </c>
       <c r="G387" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="J387" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B388" s="2">
         <v>44566</v>
       </c>
       <c r="C388" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D388" s="2">
         <v>44573</v>
@@ -11847,18 +11844,18 @@
         <v>44.1</v>
       </c>
       <c r="J388" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B389" s="2">
         <v>44566</v>
       </c>
       <c r="C389" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D389" s="2">
         <v>44594</v>
@@ -11870,18 +11867,18 @@
         <v>49.5</v>
       </c>
       <c r="J389" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B390" s="2">
         <v>44566</v>
       </c>
       <c r="C390" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D390" s="2">
         <v>44573</v>
@@ -11893,18 +11890,18 @@
         <v>44.1</v>
       </c>
       <c r="J390" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B391" s="2">
         <v>44566</v>
       </c>
       <c r="C391" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D391" s="2">
         <v>44566</v>
@@ -11918,13 +11915,13 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B392" s="2">
         <v>44566</v>
       </c>
       <c r="C392" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D392" s="2">
         <v>44622</v>
@@ -11938,13 +11935,13 @@
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B393" s="2">
         <v>44567</v>
       </c>
       <c r="C393" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D393" s="2">
         <v>44574</v>
@@ -11956,18 +11953,18 @@
         <v>33.1</v>
       </c>
       <c r="J393" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B394" s="2">
         <v>44567</v>
       </c>
       <c r="C394" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D394" s="2">
         <v>44595</v>
@@ -11979,18 +11976,18 @@
         <v>49.6</v>
       </c>
       <c r="J394" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B395" s="2">
         <v>44567</v>
       </c>
       <c r="C395" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D395" s="2">
         <v>44595</v>
@@ -12002,32 +11999,32 @@
         <v>45.9</v>
       </c>
       <c r="J395" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B396" s="2">
         <v>44567</v>
       </c>
       <c r="C396" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="J396" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B397" s="2">
         <v>44571</v>
       </c>
       <c r="C397" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D397" s="2">
         <v>44580</v>
@@ -12036,21 +12033,21 @@
         <v>2340</v>
       </c>
       <c r="F397" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J397" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B398" s="2">
         <v>44571</v>
       </c>
       <c r="C398" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D398" s="2">
         <v>44585</v>
@@ -12059,46 +12056,46 @@
         <v>46.2</v>
       </c>
       <c r="J398" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B399" s="2">
         <v>44571</v>
       </c>
       <c r="C399" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="J399" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B400" s="2">
         <v>44571</v>
       </c>
       <c r="C400" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="J400" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B401" s="2">
         <v>44571</v>
       </c>
       <c r="C401" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D401" s="2">
         <v>44627</v>
@@ -12110,18 +12107,18 @@
         <v>54.6</v>
       </c>
       <c r="J401" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B402" s="2">
         <v>44572</v>
       </c>
       <c r="C402" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D402" s="2">
         <v>44580</v>
@@ -12130,21 +12127,21 @@
         <v>2350</v>
       </c>
       <c r="F402" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J402" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B403" s="2">
         <v>44572</v>
       </c>
       <c r="C403" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D403" s="2">
         <v>44600</v>
@@ -12156,18 +12153,18 @@
         <v>36.9</v>
       </c>
       <c r="J403" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B404" s="2">
         <v>44572</v>
       </c>
       <c r="C404" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D404" s="2">
         <v>44601</v>
@@ -12179,18 +12176,18 @@
         <v>40.9</v>
       </c>
       <c r="J404" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B405" s="2">
         <v>44572</v>
       </c>
       <c r="C405" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D405" s="2">
         <v>44628</v>
@@ -12202,18 +12199,18 @@
         <v>46.9</v>
       </c>
       <c r="J405" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B406" s="2">
         <v>44573</v>
       </c>
       <c r="C406" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D406" s="2">
         <v>44580</v>
@@ -12225,18 +12222,18 @@
         <v>35.200000000000003</v>
       </c>
       <c r="J406" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B407" s="2">
         <v>44573</v>
       </c>
       <c r="C407" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D407" s="2">
         <v>44601</v>
@@ -12248,18 +12245,18 @@
         <v>46.7</v>
       </c>
       <c r="J407" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B408" s="2">
         <v>44573</v>
       </c>
       <c r="C408" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D408" s="2">
         <v>44573</v>
@@ -12271,32 +12268,32 @@
         <v>50.5</v>
       </c>
       <c r="J408" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B409" s="2">
         <v>44573</v>
       </c>
       <c r="C409" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J409" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B410" s="2">
         <v>44574</v>
       </c>
       <c r="C410" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D410" s="2">
         <v>44581</v>
@@ -12310,13 +12307,13 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B411" s="2">
         <v>44574</v>
       </c>
       <c r="C411" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D411" s="2">
         <v>44602</v>
@@ -12330,13 +12327,13 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B412" s="2">
         <v>44574</v>
       </c>
       <c r="C412" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D412" s="2">
         <v>44602</v>
@@ -12350,33 +12347,33 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B413" s="2">
         <v>44574</v>
       </c>
       <c r="C413" t="s">
-        <v>595</v>
-      </c>
-      <c r="D413" t="s">
+        <v>594</v>
+      </c>
+      <c r="D413" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E413" t="s">
         <v>598</v>
       </c>
-      <c r="E413" t="s">
+      <c r="I413" t="s">
         <v>599</v>
-      </c>
-      <c r="I413" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B414" s="2">
         <v>44575</v>
       </c>
       <c r="C414" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D414" s="2">
         <v>44582</v>
@@ -12390,13 +12387,13 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B415" s="2">
         <v>44575</v>
       </c>
       <c r="C415" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D415" s="2">
         <v>44603</v>
@@ -12410,13 +12407,13 @@
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B416" s="2">
         <v>44575</v>
       </c>
       <c r="C416" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D416" s="2">
         <v>44603</v>
@@ -12430,33 +12427,33 @@
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B417" s="2">
         <v>44575</v>
       </c>
       <c r="C417" t="s">
-        <v>606</v>
-      </c>
-      <c r="D417" t="s">
+        <v>605</v>
+      </c>
+      <c r="D417" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E417" t="s">
         <v>608</v>
       </c>
-      <c r="E417" t="s">
+      <c r="I417" t="s">
         <v>609</v>
-      </c>
-      <c r="I417" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B418" s="2">
         <v>44578</v>
       </c>
       <c r="C418" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D418" s="2">
         <v>44587</v>
@@ -12465,18 +12462,18 @@
         <v>2380</v>
       </c>
       <c r="F418" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B419" s="2">
         <v>44578</v>
       </c>
       <c r="C419" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D419" s="2">
         <v>44606</v>
@@ -12490,13 +12487,13 @@
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B420" s="2">
         <v>44578</v>
       </c>
       <c r="C420" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D420" s="2">
         <v>44606</v>
@@ -12510,33 +12507,33 @@
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B421" s="2">
         <v>44578</v>
       </c>
       <c r="C421" t="s">
-        <v>612</v>
-      </c>
-      <c r="D421" t="s">
-        <v>617</v>
+        <v>611</v>
+      </c>
+      <c r="D421" s="2" t="s">
+        <v>616</v>
       </c>
       <c r="E421">
         <v>2380</v>
       </c>
       <c r="I421" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B422" s="2">
         <v>44578</v>
       </c>
       <c r="C422" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D422" s="2">
         <v>44587</v>
@@ -12545,18 +12542,18 @@
         <v>2370</v>
       </c>
       <c r="F422" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B423" s="2">
         <v>44578</v>
       </c>
       <c r="C423" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D423" s="2">
         <v>44606</v>
@@ -12570,44 +12567,44 @@
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B424" s="2">
         <v>44578</v>
       </c>
       <c r="C424" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B425" s="2">
         <v>44578</v>
       </c>
       <c r="C425" t="s">
-        <v>627</v>
-      </c>
-      <c r="D425" t="s">
-        <v>617</v>
+        <v>626</v>
+      </c>
+      <c r="D425" s="2" t="s">
+        <v>616</v>
       </c>
       <c r="E425">
         <v>2370</v>
       </c>
       <c r="I425" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B426" s="2">
         <v>44579</v>
       </c>
       <c r="C426" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D426" s="2">
         <v>44587</v>
@@ -12616,18 +12613,18 @@
         <v>2390</v>
       </c>
       <c r="F426" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B427" s="2">
         <v>44579</v>
       </c>
       <c r="C427" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D427" s="2">
         <v>44607</v>
@@ -12641,13 +12638,13 @@
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B428" s="2">
         <v>44579</v>
       </c>
       <c r="C428" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D428" s="2">
         <v>44607</v>
@@ -12661,13 +12658,13 @@
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B429" s="2">
         <v>44580</v>
       </c>
       <c r="C429" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D429" s="2">
         <v>44587</v>
@@ -12681,13 +12678,13 @@
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B430" s="2">
         <v>44580</v>
       </c>
       <c r="C430" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D430" s="2">
         <v>44608</v>
@@ -12701,13 +12698,13 @@
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B431" s="2">
         <v>44580</v>
       </c>
       <c r="C431" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D431" s="2">
         <v>44608</v>
@@ -12721,24 +12718,24 @@
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B432" s="2">
         <v>44580</v>
       </c>
       <c r="C432" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B433" s="2">
         <v>44581</v>
       </c>
       <c r="C433" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D433" s="2">
         <v>44588</v>
@@ -12752,13 +12749,13 @@
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B434" s="2">
         <v>44581</v>
       </c>
       <c r="C434" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D434" s="2">
         <v>44588</v>
@@ -12772,13 +12769,13 @@
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B435" s="2">
         <v>44581</v>
       </c>
       <c r="C435" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D435" s="2">
         <v>44609</v>
@@ -12792,13 +12789,13 @@
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B436" s="2">
         <v>44581</v>
       </c>
       <c r="C436" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D436" s="2">
         <v>44609</v>
@@ -12812,35 +12809,35 @@
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B437" s="2">
         <v>44581</v>
       </c>
       <c r="C437" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B438" s="2">
         <v>44581</v>
       </c>
       <c r="C438" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B439" s="2">
         <v>44582</v>
       </c>
       <c r="C439" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D439" s="2">
         <v>44589</v>
@@ -12854,13 +12851,13 @@
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B440" s="2">
         <v>44582</v>
       </c>
       <c r="C440" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D440" s="2">
         <v>44610</v>
@@ -12874,13 +12871,13 @@
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B441" s="2">
         <v>44582</v>
       </c>
       <c r="C441" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D441" s="2">
         <v>44610</v>
@@ -12894,24 +12891,24 @@
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B442" s="2">
         <v>44582</v>
       </c>
       <c r="C442" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B443" s="2">
         <v>44585</v>
       </c>
       <c r="C443" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D443" s="2">
         <v>44594</v>
@@ -12920,18 +12917,18 @@
         <v>2380</v>
       </c>
       <c r="F443" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B444" s="2">
         <v>44585</v>
       </c>
       <c r="C444" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D444" s="2">
         <v>44613</v>
@@ -12945,13 +12942,13 @@
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B445" s="2">
         <v>44585</v>
       </c>
       <c r="C445" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D445" s="2">
         <v>44613</v>
@@ -12965,44 +12962,44 @@
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B446" s="2">
         <v>44585</v>
       </c>
       <c r="C446" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B447" s="2">
         <v>44586</v>
       </c>
       <c r="C447" t="s">
-        <v>664</v>
-      </c>
-      <c r="D447">
+        <v>663</v>
+      </c>
+      <c r="D447" s="2">
         <v>8004</v>
       </c>
       <c r="E447">
         <v>2330</v>
       </c>
       <c r="F447" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B448" s="2">
         <v>44586</v>
       </c>
       <c r="C448" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D448" s="2">
         <v>44614</v>
@@ -13016,13 +13013,13 @@
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B449" s="2">
         <v>44586</v>
       </c>
       <c r="C449" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D449" s="2">
         <v>44614</v>
@@ -13036,24 +13033,24 @@
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B450" s="2">
         <v>44586</v>
       </c>
       <c r="C450" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B451" s="2">
         <v>44587</v>
       </c>
       <c r="C451" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D451" s="2">
         <v>44594</v>
@@ -13067,46 +13064,46 @@
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B452" s="2">
         <v>44587</v>
       </c>
       <c r="C452" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B453" s="2">
         <v>44587</v>
       </c>
       <c r="C453" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B454" s="2">
         <v>44587</v>
       </c>
       <c r="C454" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B455" s="2">
         <v>44588</v>
       </c>
       <c r="C455" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D455" s="2">
         <v>44595</v>
@@ -13120,13 +13117,13 @@
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B456" s="2">
         <v>44588</v>
       </c>
       <c r="C456" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D456" s="2">
         <v>44616</v>
@@ -13140,13 +13137,13 @@
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B457" s="2">
         <v>44588</v>
       </c>
       <c r="C457" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D457" s="2">
         <v>44616</v>
@@ -13160,24 +13157,24 @@
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B458" s="2">
         <v>44588</v>
       </c>
       <c r="C458" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B459" s="2">
         <v>44589</v>
       </c>
       <c r="C459" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D459" s="2">
         <v>44596</v>
@@ -13191,13 +13188,13 @@
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B460" s="2">
         <v>44589</v>
       </c>
       <c r="C460" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D460" s="2">
         <v>44596</v>
@@ -13211,13 +13208,13 @@
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B461" s="2">
         <v>44589</v>
       </c>
       <c r="C461" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D461" s="2">
         <v>44617</v>
@@ -13231,13 +13228,13 @@
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B462" s="2">
         <v>44589</v>
       </c>
       <c r="C462" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D462" s="2">
         <v>44617</v>
@@ -13251,24 +13248,24 @@
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B463" s="2">
         <v>44589</v>
       </c>
       <c r="C463" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B464" s="2">
         <v>44592</v>
       </c>
       <c r="C464" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D464" s="2">
         <v>44601</v>
@@ -13277,51 +13274,51 @@
         <v>2370</v>
       </c>
       <c r="F464" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B465" s="2">
         <v>44592</v>
       </c>
       <c r="C465" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B466" s="2">
         <v>44592</v>
       </c>
       <c r="C466" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B467" s="2">
         <v>44592</v>
       </c>
       <c r="C467" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B468" s="2">
         <v>44592</v>
       </c>
       <c r="C468" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D468" s="2">
         <v>44601</v>
@@ -13330,18 +13327,18 @@
         <v>2340</v>
       </c>
       <c r="F468" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B469" s="2">
         <v>44592</v>
       </c>
       <c r="C469" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D469" s="2">
         <v>44601</v>
@@ -13350,51 +13347,51 @@
         <v>2340</v>
       </c>
       <c r="F469" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B470" s="2">
         <v>44592</v>
       </c>
       <c r="C470" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B471" s="2">
         <v>44592</v>
       </c>
       <c r="C471" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B472" s="2">
         <v>44592</v>
       </c>
       <c r="C472" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B473" s="2">
         <v>44594</v>
       </c>
       <c r="C473" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D473" s="2">
         <v>44601</v>
@@ -13408,13 +13405,13 @@
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B474" s="2">
         <v>44594</v>
       </c>
       <c r="C474" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D474" s="2">
         <v>44622</v>
@@ -13428,13 +13425,13 @@
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B475" s="2">
         <v>44594</v>
       </c>
       <c r="C475" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D475" s="2">
         <v>44622</v>
@@ -13448,24 +13445,24 @@
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B476" s="2">
         <v>44594</v>
       </c>
       <c r="C476" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B477" s="2">
         <v>44595</v>
       </c>
       <c r="C477" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D477" s="2">
         <v>44602</v>
@@ -13479,13 +13476,13 @@
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B478" s="2">
         <v>44595</v>
       </c>
       <c r="C478" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D478" s="2">
         <v>44623</v>
@@ -13499,13 +13496,13 @@
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B479" s="2">
         <v>44595</v>
       </c>
       <c r="C479" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D479" s="2">
         <v>44623</v>
@@ -13519,24 +13516,24 @@
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B480" s="2">
         <v>44595</v>
       </c>
       <c r="C480" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B481" s="2">
         <v>44596</v>
       </c>
       <c r="C481" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D481" s="2">
         <v>44603</v>
@@ -13550,13 +13547,13 @@
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B482" s="2">
         <v>44596</v>
       </c>
       <c r="C482" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D482" s="2">
         <v>44624</v>
@@ -13570,13 +13567,13 @@
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B483" s="2">
         <v>44596</v>
       </c>
       <c r="C483" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D483" s="2">
         <v>44596</v>
@@ -13590,18 +13587,18 @@
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
+        <v>713</v>
+      </c>
+      <c r="B485" s="2">
+        <v>44599</v>
+      </c>
+      <c r="C485" t="s">
         <v>714</v>
-      </c>
-      <c r="B485" s="3">
-        <v>44599</v>
-      </c>
-      <c r="C485" t="s">
-        <v>715</v>
       </c>
       <c r="D485" s="2">
         <v>44608</v>
@@ -13610,18 +13607,18 @@
         <v>2310</v>
       </c>
       <c r="F485" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
+        <v>716</v>
+      </c>
+      <c r="B486" s="2">
+        <v>44599</v>
+      </c>
+      <c r="C486" t="s">
         <v>717</v>
-      </c>
-      <c r="B486" s="3">
-        <v>44599</v>
-      </c>
-      <c r="C486" t="s">
-        <v>718</v>
       </c>
       <c r="D486" s="2">
         <v>44627</v>
@@ -13635,13 +13632,13 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
+        <v>718</v>
+      </c>
+      <c r="B487" s="2">
+        <v>44599</v>
+      </c>
+      <c r="C487" t="s">
         <v>719</v>
-      </c>
-      <c r="B487" s="3">
-        <v>44599</v>
-      </c>
-      <c r="C487" t="s">
-        <v>720</v>
       </c>
       <c r="D487" s="2">
         <v>44627</v>
@@ -13655,24 +13652,24 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
+        <v>720</v>
+      </c>
+      <c r="B488" s="2">
+        <v>44599</v>
+      </c>
+      <c r="C488" t="s">
         <v>721</v>
-      </c>
-      <c r="B488" s="3">
-        <v>44599</v>
-      </c>
-      <c r="C488" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B489" s="2">
         <v>44600</v>
       </c>
       <c r="C489" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D489" s="2">
         <v>44608</v>
@@ -13681,18 +13678,18 @@
         <v>2350</v>
       </c>
       <c r="F489" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B490" s="2">
         <v>44600</v>
       </c>
       <c r="C490" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D490" s="2">
         <v>44628</v>
@@ -13706,13 +13703,13 @@
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B491" s="2">
         <v>44600</v>
       </c>
       <c r="C491" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D491" s="2">
         <v>44628</v>
@@ -13726,24 +13723,24 @@
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B492" s="2">
         <v>44600</v>
       </c>
       <c r="C492" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B493" s="2">
         <v>44600</v>
       </c>
       <c r="C493" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D493" s="2">
         <v>44608</v>
@@ -13752,18 +13749,18 @@
         <v>2360</v>
       </c>
       <c r="F493" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B494" s="2">
         <v>44600</v>
       </c>
       <c r="C494" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D494" s="2">
         <v>44628</v>
@@ -13777,13 +13774,13 @@
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B495" s="2">
         <v>44600</v>
       </c>
       <c r="C495" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D495" s="2">
         <v>44628</v>
@@ -13797,24 +13794,24 @@
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B496" s="2">
         <v>44600</v>
       </c>
       <c r="C496" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B497" s="2">
         <v>44601</v>
       </c>
       <c r="C497" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D497" s="2">
         <v>44608</v>
@@ -13823,69 +13820,69 @@
         <v>2390</v>
       </c>
       <c r="F497" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B498" s="2">
         <v>44601</v>
       </c>
       <c r="C498" t="s">
+        <v>740</v>
+      </c>
+      <c r="D498" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="D498" t="s">
+      <c r="E498" t="s">
         <v>742</v>
       </c>
-      <c r="E498" t="s">
+      <c r="H498" t="s">
         <v>743</v>
-      </c>
-      <c r="H498" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B499" s="2">
         <v>44601</v>
       </c>
       <c r="C499" t="s">
+        <v>745</v>
+      </c>
+      <c r="D499" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E499" t="s">
         <v>746</v>
       </c>
-      <c r="D499" t="s">
-        <v>742</v>
-      </c>
-      <c r="E499" t="s">
+      <c r="H499" t="s">
         <v>747</v>
-      </c>
-      <c r="H499" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B500" s="2">
         <v>44601</v>
       </c>
       <c r="C500" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B501" s="2">
         <v>44602</v>
       </c>
       <c r="C501" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D501" s="2">
         <v>44616</v>
@@ -13899,64 +13896,64 @@
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B502" s="2">
         <v>44602</v>
       </c>
       <c r="C502" t="s">
-        <v>751</v>
-      </c>
-      <c r="D502" t="s">
-        <v>598</v>
+        <v>750</v>
+      </c>
+      <c r="D502" s="2" t="s">
+        <v>597</v>
       </c>
       <c r="E502" t="s">
+        <v>752</v>
+      </c>
+      <c r="H502" t="s">
         <v>753</v>
-      </c>
-      <c r="H502" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B503" s="2">
         <v>44602</v>
       </c>
       <c r="C503" t="s">
-        <v>751</v>
-      </c>
-      <c r="D503" t="s">
-        <v>598</v>
+        <v>750</v>
+      </c>
+      <c r="D503" s="2" t="s">
+        <v>597</v>
       </c>
       <c r="E503" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H503" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B504" s="2">
         <v>44602</v>
       </c>
       <c r="C504" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B505" s="2">
         <v>44603</v>
       </c>
       <c r="C505" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D505" s="2">
         <v>44615</v>
@@ -13970,13 +13967,13 @@
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B506" s="2">
         <v>44603</v>
       </c>
       <c r="C506" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D506" s="2">
         <v>44617</v>
@@ -13990,16 +13987,16 @@
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B507" s="2">
         <v>44603</v>
       </c>
       <c r="C507" t="s">
-        <v>759</v>
-      </c>
-      <c r="D507" t="s">
-        <v>608</v>
+        <v>758</v>
+      </c>
+      <c r="D507" s="2" t="s">
+        <v>607</v>
       </c>
       <c r="E507">
         <v>2360</v>
@@ -14010,16 +14007,16 @@
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B508" s="2">
         <v>44603</v>
       </c>
       <c r="C508" t="s">
-        <v>759</v>
-      </c>
-      <c r="D508" t="s">
-        <v>608</v>
+        <v>758</v>
+      </c>
+      <c r="D508" s="2" t="s">
+        <v>607</v>
       </c>
       <c r="E508">
         <v>2370</v>
@@ -14030,24 +14027,24 @@
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B509" s="2">
         <v>44603</v>
       </c>
       <c r="C509" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B510" s="2">
         <v>44606</v>
       </c>
       <c r="C510" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D510" s="2">
         <v>44615</v>
@@ -14061,16 +14058,16 @@
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B511" s="2">
         <v>44606</v>
       </c>
       <c r="C511" t="s">
-        <v>764</v>
-      </c>
-      <c r="D511" t="s">
-        <v>617</v>
+        <v>763</v>
+      </c>
+      <c r="D511" s="2" t="s">
+        <v>616</v>
       </c>
       <c r="E511">
         <v>2330</v>
@@ -14081,16 +14078,16 @@
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B512" s="2">
         <v>44606</v>
       </c>
       <c r="C512" t="s">
-        <v>764</v>
-      </c>
-      <c r="D512" t="s">
-        <v>617</v>
+        <v>763</v>
+      </c>
+      <c r="D512" s="2" t="s">
+        <v>616</v>
       </c>
       <c r="E512">
         <v>2330</v>
@@ -14101,38 +14098,38 @@
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B513" s="2">
         <v>44606</v>
       </c>
       <c r="C513" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B514" s="2">
         <v>44606</v>
       </c>
       <c r="C514" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B515" s="2">
         <v>44606</v>
       </c>
       <c r="C515" t="s">
-        <v>769</v>
-      </c>
-      <c r="D515" t="s">
-        <v>617</v>
+        <v>768</v>
+      </c>
+      <c r="D515" s="2" t="s">
+        <v>616</v>
       </c>
       <c r="E515">
         <v>2380</v>
@@ -14143,16 +14140,16 @@
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B516" s="2">
         <v>44606</v>
       </c>
       <c r="C516" t="s">
-        <v>769</v>
-      </c>
-      <c r="D516" t="s">
-        <v>617</v>
+        <v>768</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>616</v>
       </c>
       <c r="E516">
         <v>2380</v>
@@ -14163,888 +14160,888 @@
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B517" s="2">
         <v>44606</v>
       </c>
       <c r="C517" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B518" s="2">
         <v>44607</v>
       </c>
       <c r="C518" t="s">
+        <v>773</v>
+      </c>
+      <c r="D518" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E518" t="s">
+        <v>598</v>
+      </c>
+      <c r="F518" t="s">
         <v>774</v>
-      </c>
-      <c r="D518" t="s">
-        <v>742</v>
-      </c>
-      <c r="E518" t="s">
-        <v>599</v>
-      </c>
-      <c r="F518" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B519" s="2">
         <v>44607</v>
       </c>
       <c r="C519" t="s">
-        <v>774</v>
-      </c>
-      <c r="D519" t="s">
+        <v>773</v>
+      </c>
+      <c r="D519" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="E519" t="s">
+        <v>608</v>
+      </c>
+      <c r="H519" t="s">
         <v>777</v>
-      </c>
-      <c r="E519" t="s">
-        <v>609</v>
-      </c>
-      <c r="H519" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B520" s="2">
         <v>44607</v>
       </c>
       <c r="C520" t="s">
-        <v>774</v>
-      </c>
-      <c r="D520" t="s">
-        <v>777</v>
+        <v>773</v>
+      </c>
+      <c r="D520" s="2" t="s">
+        <v>776</v>
       </c>
       <c r="E520" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H520" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B521" s="2">
         <v>44607</v>
       </c>
       <c r="C521" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B522" s="2">
         <v>44608</v>
       </c>
       <c r="C522" t="s">
+        <v>782</v>
+      </c>
+      <c r="D522" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E522" t="s">
+        <v>752</v>
+      </c>
+      <c r="F522" t="s">
         <v>783</v>
-      </c>
-      <c r="D522" t="s">
-        <v>742</v>
-      </c>
-      <c r="E522" t="s">
-        <v>753</v>
-      </c>
-      <c r="F522" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B523" s="2">
         <v>44608</v>
       </c>
       <c r="C523" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B524" s="2">
         <v>44608</v>
       </c>
       <c r="C524" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B525" s="2">
         <v>44608</v>
       </c>
       <c r="C525" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B526" s="2">
         <v>44609</v>
       </c>
       <c r="C526" t="s">
+        <v>788</v>
+      </c>
+      <c r="D526" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E526" t="s">
+        <v>752</v>
+      </c>
+      <c r="F526" t="s">
         <v>789</v>
-      </c>
-      <c r="D526" t="s">
-        <v>742</v>
-      </c>
-      <c r="E526" t="s">
-        <v>753</v>
-      </c>
-      <c r="F526" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B527" s="2">
         <v>44609</v>
       </c>
       <c r="C527" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B528" s="2">
         <v>44609</v>
       </c>
       <c r="C528" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B529" s="2">
         <v>44609</v>
       </c>
       <c r="C529" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B530" s="2">
         <v>44610</v>
       </c>
       <c r="C530" t="s">
+        <v>794</v>
+      </c>
+      <c r="D530" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E530" t="s">
+        <v>752</v>
+      </c>
+      <c r="F530" t="s">
         <v>795</v>
-      </c>
-      <c r="D530" t="s">
-        <v>742</v>
-      </c>
-      <c r="E530" t="s">
-        <v>753</v>
-      </c>
-      <c r="F530" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B531" s="2">
         <v>44610</v>
       </c>
       <c r="C531" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B532" s="2">
         <v>44610</v>
       </c>
       <c r="C532" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B533" s="2">
         <v>44610</v>
       </c>
       <c r="C533" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B534" s="2">
         <v>44613</v>
       </c>
       <c r="C534" t="s">
+        <v>800</v>
+      </c>
+      <c r="D534" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E534" t="s">
         <v>801</v>
       </c>
-      <c r="D534" t="s">
-        <v>742</v>
-      </c>
-      <c r="E534" t="s">
+      <c r="F534" t="s">
         <v>802</v>
-      </c>
-      <c r="F534" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B535" s="2">
         <v>44613</v>
       </c>
       <c r="C535" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B536" s="2">
         <v>44613</v>
       </c>
       <c r="C536" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B537" s="2">
         <v>44613</v>
       </c>
       <c r="C537" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B538" s="2">
         <v>44614</v>
       </c>
       <c r="C538" t="s">
+        <v>807</v>
+      </c>
+      <c r="D538" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E538" t="s">
         <v>808</v>
       </c>
-      <c r="D538" t="s">
-        <v>742</v>
-      </c>
-      <c r="E538" t="s">
+      <c r="F538" t="s">
         <v>809</v>
-      </c>
-      <c r="F538" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B539" s="2">
         <v>44614</v>
       </c>
       <c r="C539" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B540" s="2">
         <v>44614</v>
       </c>
       <c r="C540" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B541" s="2">
         <v>44614</v>
       </c>
       <c r="C541" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B542" s="2">
         <v>44614</v>
       </c>
       <c r="C542" t="s">
+        <v>814</v>
+      </c>
+      <c r="D542" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E542" t="s">
+        <v>742</v>
+      </c>
+      <c r="F542" t="s">
         <v>815</v>
-      </c>
-      <c r="D542" t="s">
-        <v>742</v>
-      </c>
-      <c r="E542" t="s">
-        <v>743</v>
-      </c>
-      <c r="F542" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B543" s="2">
         <v>44614</v>
       </c>
       <c r="C543" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B544" s="2">
         <v>44614</v>
       </c>
       <c r="C544" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B545" s="2">
         <v>44614</v>
       </c>
       <c r="C545" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B546" s="2">
         <v>44615</v>
       </c>
       <c r="C546" t="s">
+        <v>820</v>
+      </c>
+      <c r="D546" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E546" t="s">
+        <v>801</v>
+      </c>
+      <c r="G546" t="s">
         <v>821</v>
-      </c>
-      <c r="D546" t="s">
-        <v>742</v>
-      </c>
-      <c r="E546" t="s">
-        <v>802</v>
-      </c>
-      <c r="G546" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B547" s="2">
         <v>44615</v>
       </c>
       <c r="C547" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B548" s="2">
         <v>44615</v>
       </c>
       <c r="C548" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B549" s="2">
         <v>44615</v>
       </c>
       <c r="C549" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B550" s="2">
         <v>44616</v>
       </c>
       <c r="C550" t="s">
+        <v>826</v>
+      </c>
+      <c r="D550" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E550" t="s">
+        <v>608</v>
+      </c>
+      <c r="F550" t="s">
         <v>827</v>
-      </c>
-      <c r="D550" t="s">
-        <v>742</v>
-      </c>
-      <c r="E550" t="s">
-        <v>609</v>
-      </c>
-      <c r="F550" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B551" s="2">
         <v>44616</v>
       </c>
       <c r="C551" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B552" s="2">
         <v>44616</v>
       </c>
       <c r="C552" t="s">
-        <v>827</v>
-      </c>
-      <c r="D552" t="s">
-        <v>617</v>
+        <v>826</v>
+      </c>
+      <c r="D552" s="2" t="s">
+        <v>616</v>
       </c>
       <c r="E552" t="s">
+        <v>830</v>
+      </c>
+      <c r="H552" t="s">
         <v>831</v>
-      </c>
-      <c r="H552" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B553" s="2">
         <v>44616</v>
       </c>
       <c r="C553" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B554" s="2">
         <v>44617</v>
       </c>
       <c r="C554" t="s">
+        <v>834</v>
+      </c>
+      <c r="D554" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E554" t="s">
         <v>835</v>
       </c>
-      <c r="D554" t="s">
-        <v>608</v>
-      </c>
-      <c r="E554" t="s">
+      <c r="G554" t="s">
         <v>836</v>
-      </c>
-      <c r="G554" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B555" s="2">
         <v>44617</v>
       </c>
       <c r="C555" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B556" s="2">
         <v>44617</v>
       </c>
       <c r="C556" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B557" s="2">
         <v>44617</v>
       </c>
       <c r="C557" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B558" s="2">
         <v>44620</v>
       </c>
       <c r="C558" t="s">
+        <v>841</v>
+      </c>
+      <c r="D558" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E558" t="s">
+        <v>608</v>
+      </c>
+      <c r="F558" t="s">
         <v>842</v>
-      </c>
-      <c r="D558" t="s">
-        <v>742</v>
-      </c>
-      <c r="E558" t="s">
-        <v>609</v>
-      </c>
-      <c r="F558" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B559" s="2">
         <v>44620</v>
       </c>
       <c r="C559" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B560" s="2">
         <v>44620</v>
       </c>
       <c r="C560" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B561" s="2">
         <v>44620</v>
       </c>
       <c r="C561" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B562" s="2">
         <v>44620</v>
       </c>
       <c r="C562" t="s">
+        <v>847</v>
+      </c>
+      <c r="D562" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E562" t="s">
+        <v>801</v>
+      </c>
+      <c r="F562" t="s">
         <v>848</v>
-      </c>
-      <c r="D562" t="s">
-        <v>742</v>
-      </c>
-      <c r="E562" t="s">
-        <v>802</v>
-      </c>
-      <c r="F562" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B563" s="2">
         <v>44620</v>
       </c>
       <c r="C563" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B564" s="2">
         <v>44620</v>
       </c>
       <c r="C564" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B565" s="2">
         <v>44620</v>
       </c>
       <c r="C565" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B566" s="2">
         <v>44621</v>
       </c>
       <c r="C566" t="s">
+        <v>853</v>
+      </c>
+      <c r="D566" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E566" t="s">
+        <v>598</v>
+      </c>
+      <c r="F566" t="s">
         <v>854</v>
-      </c>
-      <c r="D566" t="s">
-        <v>742</v>
-      </c>
-      <c r="E566" t="s">
-        <v>599</v>
-      </c>
-      <c r="F566" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B567" s="2">
         <v>44621</v>
       </c>
       <c r="C567" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B568" s="2">
         <v>44621</v>
       </c>
       <c r="C568" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B569" s="2">
         <v>44621</v>
       </c>
       <c r="C569" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B570" s="2">
         <v>44622</v>
       </c>
       <c r="C570" t="s">
+        <v>859</v>
+      </c>
+      <c r="D570" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E570" t="s">
+        <v>608</v>
+      </c>
+      <c r="F570" t="s">
         <v>860</v>
-      </c>
-      <c r="D570" t="s">
-        <v>742</v>
-      </c>
-      <c r="E570" t="s">
-        <v>609</v>
-      </c>
-      <c r="F570" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B571" s="2">
         <v>44622</v>
       </c>
       <c r="C571" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B572" s="2">
         <v>44622</v>
       </c>
       <c r="C572" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B573" s="2">
         <v>44622</v>
       </c>
       <c r="C573" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B574" s="2">
         <v>44623</v>
       </c>
       <c r="C574" t="s">
+        <v>865</v>
+      </c>
+      <c r="D574" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E574" t="s">
+        <v>598</v>
+      </c>
+      <c r="F574" t="s">
         <v>866</v>
-      </c>
-      <c r="D574" t="s">
-        <v>598</v>
-      </c>
-      <c r="E574" t="s">
-        <v>599</v>
-      </c>
-      <c r="F574" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B575" s="2">
         <v>44623</v>
       </c>
       <c r="C575" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B576" s="2">
         <v>44623</v>
       </c>
       <c r="C576" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B577" s="2">
         <v>44623</v>
       </c>
       <c r="C577" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B578" s="2">
         <v>44624</v>
       </c>
       <c r="C578" t="s">
+        <v>871</v>
+      </c>
+      <c r="D578" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E578" t="s">
+        <v>752</v>
+      </c>
+      <c r="F578" t="s">
         <v>872</v>
-      </c>
-      <c r="D578" t="s">
-        <v>608</v>
-      </c>
-      <c r="E578" t="s">
-        <v>753</v>
-      </c>
-      <c r="F578" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B579" s="2">
         <v>44624</v>
       </c>
       <c r="C579" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B580" s="2">
         <v>44624</v>
       </c>
       <c r="C580" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B581" s="2">
         <v>44624</v>
       </c>
       <c r="C581" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
   </sheetData>
